--- a/output/pdf_financials_xlsx/INFI.xlsx
+++ b/output/pdf_financials_xlsx/INFI.xlsx
@@ -4554,13 +4554,13 @@
         <v>1.042628</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.056952</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.517301</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.312033</v>
       </c>
     </row>
     <row r="93">
@@ -7236,7 +7236,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10354,7 +10358,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INFI.xlsx
+++ b/output/pdf_financials_xlsx/INFI.xlsx
@@ -2120,37 +2120,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.264692</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.247116</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.247116</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.155079</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.051842</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.820705</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.135277</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.812783</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.130789</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.120347</v>
       </c>
     </row>
     <row r="35">
@@ -2200,37 +2200,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.264692</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.247116</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.247116</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.155079</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.051842</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.820705</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.135277</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.812783</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.000433</v>
+        <v>0.130356</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.454489</v>
+        <v>1.574836</v>
       </c>
     </row>
     <row r="37">
@@ -2680,37 +2680,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.267506</v>
+        <v>0.002814</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.249626</v>
+        <v>0.00251</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.249626</v>
+        <v>0.00251</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.156811</v>
+        <v>0.001732</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.051842</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.820705</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.148899</v>
+        <v>0.013622</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.943101</v>
+        <v>0.130318</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.155935</v>
+        <v>0.025146</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.125524</v>
+        <v>0.005177</v>
       </c>
     </row>
     <row r="49">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E426" s="5" t="n">

--- a/output/pdf_financials_xlsx/INFI.xlsx
+++ b/output/pdf_financials_xlsx/INFI.xlsx
@@ -4845,10 +4845,10 @@
         <v>0.009552</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.036137</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.046494</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
@@ -24796,7 +24796,11 @@
           <t>Depreciation of right-of-use asset 7</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -24865,7 +24869,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -26594,7 +26602,11 @@
           <t>Depreciation of property, plant and equipment 5</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -26663,7 +26675,11 @@
           <t>Depreciation of right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INFI.xlsx
+++ b/output/pdf_financials_xlsx/INFI.xlsx
@@ -4882,22 +4882,22 @@
         <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011577</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-0.057726</v>
+        <v>-0.052542</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.010476</v>
+        <v>0.016869</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007098</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.000738</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
     </row>
     <row r="102">
@@ -5082,22 +5082,22 @@
         <v>0.072394</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.127677</v>
+        <v>0.1161</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.301006</v>
+        <v>-0.295822</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.009164</v>
+        <v>-0.002771</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.100417</v>
+        <v>0.093319</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.005272</v>
+        <v>-0.004534</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.144176</v>
+        <v>0.144294</v>
       </c>
     </row>
     <row r="107">
@@ -5454,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.004599</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -21500,7 +21500,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -21928,7 +21932,11 @@
           <t>Net proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -23220,7 +23228,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -23733,7 +23745,11 @@
           <t>Net cash generated from investing activities</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -25567,7 +25583,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -28385,7 +28405,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -29669,7 +29693,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -34442,7 +34470,11 @@
           <t>Income tax recovery -</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
